--- a/Zoning_Workbook.xlsx
+++ b/Zoning_Workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/055abc5dbe1424b0/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="254" documentId="8_{8AA4DF28-16B8-4606-B3D8-82A740A57BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C68759DE-1CC9-43D9-A3C8-F50A309ABA09}"/>
+  <xr:revisionPtr revIDLastSave="318" documentId="8_{8AA4DF28-16B8-4606-B3D8-82A740A57BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF74B6E7-9245-4D0D-8BEC-BFA6FCA03909}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3F8FDE9A-8AA9-43D2-80E0-CEBDCEE92368}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{3F8FDE9A-8AA9-43D2-80E0-CEBDCEE92368}"/>
   </bookViews>
   <sheets>
     <sheet name="Frederick County" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Montgomery County" sheetId="4" r:id="rId4"/>
     <sheet name="Garrett County" sheetId="5" r:id="rId5"/>
     <sheet name="Howard County" sheetId="6" r:id="rId6"/>
+    <sheet name="Carroll County" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="365">
   <si>
     <t>Zone</t>
   </si>
@@ -1216,6 +1217,108 @@
   </si>
   <si>
     <t>The TNC District is intended to provide for the development of pedestrian-oriented, urban activity centers with a mix of retail, service, office and residential uses. These centers should be located near Route 40 and close to residential communities that will benefit from a pedestrian-oriented local business area. The requirements of this district, in conjunction with the Route 40 Manual and the public improvements recommended by the Route 40 Enhancement Study, will result in development that will strengthen nearby communities, provide for safe and convenient pedestrian travel, and improve the streetscape of Route 40 and intersecting roads. Sites within the TNC Overlay may continue to be used, developed and redeveloped in accordance with the underlying zoning. The intent of this district is to provide an alternative method of development for property owners who choose to comply with the Route 40 Manual and the requirements of this district. Development complying with the TNC District requirements will be permitted to include residential development and will have greater flexibility in some bulk requirements.</t>
+  </si>
+  <si>
+    <t>Carroll County Planning and Zoning Department</t>
+  </si>
+  <si>
+    <t>The purpose of the Agricultural District is to provide locations generally outside of the designated growth areas where agriculture is the primary land use. Residential development potential is generally limited to one single-family or two-family dwelling for every 20 acres. Commercial and industrial uses are limited to agribusiness, agritourism, and those uses intended to serve the agricultural industry and residents of the area while maintaining the character of the surrounding countryside. No water and sewer service is planned to these areas.</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>The purpose of the C District is to prescribe a zoning category for those areas where, because of natural geographic factors and existing land uses, it is considered feasible and desirable to conserve open spaces, water supply sources, woodland areas, wildlife, and other natural resources. This district may include extensive steeply sloped areas, stream valleys, water supply sources, and wooded areas adjacent thereto. Industrial development should not be located in these areas, and residential development should generally be limited to one single-family detached dwelling per three acres. No water or sewer service is planned to these areas.</t>
+  </si>
+  <si>
+    <t>Residence (40,000)</t>
+  </si>
+  <si>
+    <t>R-40,000</t>
+  </si>
+  <si>
+    <t>The purpose of the R-40,000 Residence District is primarily to provide a location for single-family residential development, the individual lots of which generally contain a minimum of 40,000 square feet. This district is generally not intended to be served with public water or sewerage facilities although in special situations, it may be. The district would generally coincide with areas designated for low-density residential development on the Master Plan.</t>
+  </si>
+  <si>
+    <t>Residence (20,000)</t>
+  </si>
+  <si>
+    <t>R-20,000</t>
+  </si>
+  <si>
+    <t>The purpose of the R-20,000 District is primarily to provide a location for single-family residential development, the individual lots of which generally contain a minimum of 20,000 square feet. The area should be served with public water and/or public sewerage facilities. The district would generally coincide with areas designated for medium-density residential development on the Master Plan.</t>
+  </si>
+  <si>
+    <t>Residence (10,000)</t>
+  </si>
+  <si>
+    <t>R-10,000</t>
+  </si>
+  <si>
+    <t>The purpose of the R-10,000 District is primarily to provide a location within the designated growth areas for smaller lot sizes, generally a minimum of 10,000 square feet for single and two-family dwellings, and multi-family dwellings when included in a planned unit development. The area should be served with public water and public sewerage facilities. The district would generally coincide with areas designated for high-density residential development in the Master Plan.</t>
+  </si>
+  <si>
+    <t>Residence (7,500)</t>
+  </si>
+  <si>
+    <t>R-7,500</t>
+  </si>
+  <si>
+    <t>The purpose of the R-7,500 Residence District is primarily to provide a location within the designated growth areas for smaller lot sizes, a minimum of 7,500 square feet, and a greater number of dwellings per acre than the other residential districts. It is intended for single-family and two-family dwellings, and multi-family dwellings when included in a planned unit development. The area should be served with public water ad public sewerage facilities. The district would coincide with areas designated for high-density residential development in the Master Plan.</t>
+  </si>
+  <si>
+    <t>Mobile Home Park</t>
+  </si>
+  <si>
+    <t>MPH</t>
+  </si>
+  <si>
+    <t>The purpose of the MHP District is to prescribe a zoning category wherein mobile home parks meeting minimum development standards established by the county may be authorized in limited locations deemed appropriate and compatible within the existing neighborhood.</t>
+  </si>
+  <si>
+    <t>Commercial Low Intensity</t>
+  </si>
+  <si>
+    <t>C-1</t>
+  </si>
+  <si>
+    <t>The purpose of the C-1 District is to provide locations for small-scale, low intensity retail and service commercial uses which are intended to provide goods and services primarily serving the residents of the surrounding neighborhoods with a minimum of consumer travel and convenient auto access. Uses allowed in the C-1 District include but are not limited to retail sales and services, personnel services, medical facilities, eating establishments, recreation and entertainment, and small professional office uses.</t>
+  </si>
+  <si>
+    <t>Commercial Medium Intensity</t>
+  </si>
+  <si>
+    <t>C-2</t>
+  </si>
+  <si>
+    <t>The purpose of the C-2 District is to provide locations for a diverse range of medium-intensity retail, service and professional office uses needed by a larger population than those provided for in the C-1 District. This district is also intended to provide locations for compatible institutional and recreational uses, limited residential uses, and some of the general neighborhood uses associated with the C-1 District. Bicycle and pedestrian access are encouraged where possible to ensure compatibility with nearby neighborhoods.</t>
+  </si>
+  <si>
+    <t>Commercial High Intensity</t>
+  </si>
+  <si>
+    <t>C-3</t>
+  </si>
+  <si>
+    <t>The purpose of the C-3 District is to provide locations for high-intensity, large-scale retail businesses and destinations of a regional nature, planned business parks, clusters of commercial development, wholesale businesses, offices, and certain light processing operations. This district is also intended to provide locations for compatible institutional and recreational uses and some of the medium-intensity uses associated with the C-2 District. Uses in this district should be located in proximity to transportation infrastructure and major corridors. Developments in the C-3 District should, where possible and appropriate, facilitate pedestrian circulation.</t>
+  </si>
+  <si>
+    <t>L-1</t>
+  </si>
+  <si>
+    <t>The purpose of the I-1 District is to provide locations for certain types of nonagricultural, nonresidential, and generally nonretail commercial activities characterized by light manufacturing, assembling, fabricating, warehousing, wholesale distribution, and limited office and commercial uses which are supportive or directly related to industrial uses, which may not be as intense as those provided for in the I-2 District and which, with proper landscaping, separation, setback, and buffering, will not significantly detract from adjoining residential or commercial properties. It is intended that such districts be located in areas with access to major thoroughfares or other major modes of transportation, depending upon the specific demands of the industry being served. Industrial Parks are encouraged in this district to provide for clustering of similar industrial uses with common access and infrastructure, as well as the provision of open spaces, stormwater management, and adequate buffering.</t>
+  </si>
+  <si>
+    <t>L-2</t>
+  </si>
+  <si>
+    <t>The purpose of the I-2 District is to provide locations for certain types of nonagricultural, nonresidential, and noncommercial activities characterized by heavy manufacturing, refining, processing, or compounding of materials or products predominantly from raw materials. This district may also accommodate some of the light manufacturing uses permitted in the I-1 (Light Industrial) District. The uses associated with this district are intensive and frequently include operations that emit strong odors; loud noises; and some level or volume of dust, vibrations, smoke, soot, vapors, light, and pollution. It is intended that properties in this district be located with access to major thoroughfares or other major modes of transportation, depending on the specific demands of the industry being served. It is not the purpose of this district to promote or encourage the use of land within this district for retail services, Planned Commercial Centers, or similar uses typically expected to be located within the established commercial districts.</t>
+  </si>
+  <si>
+    <t>Employment Campus</t>
+  </si>
+  <si>
+    <t>The purpose of the EC District is to provide for and foster comprehensively planned employment centers in campus-like settings to attract employers of highly skilled workers and primarily higher paying jobs, including but not limited to research and development, institutional, office, flex space, and other light and limited industrial uses, while also providing a more flexible approach to design and development. In this district, the integration of trails, sidewalks, communal plazas, and share amenities is encouraged. An EC development may be comprised of multiple contiguous lots, the extent of which shall be depicted on individual site plans.</t>
   </si>
 </sst>
 </file>
@@ -3483,4 +3586,217 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD8CC32-81B7-4747-A486-18F3540923B3}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C5" t="s">
+        <v>331</v>
+      </c>
+      <c r="D5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>341</v>
+      </c>
+      <c r="B6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>347</v>
+      </c>
+      <c r="B8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C8" t="s">
+        <v>331</v>
+      </c>
+      <c r="D8" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>350</v>
+      </c>
+      <c r="B9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C9" t="s">
+        <v>331</v>
+      </c>
+      <c r="D9" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>353</v>
+      </c>
+      <c r="B10" t="s">
+        <v>354</v>
+      </c>
+      <c r="C10" t="s">
+        <v>331</v>
+      </c>
+      <c r="D10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>356</v>
+      </c>
+      <c r="B11" t="s">
+        <v>357</v>
+      </c>
+      <c r="C11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D11" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" t="s">
+        <v>359</v>
+      </c>
+      <c r="C12" t="s">
+        <v>331</v>
+      </c>
+      <c r="D12" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B13" t="s">
+        <v>361</v>
+      </c>
+      <c r="C13" t="s">
+        <v>331</v>
+      </c>
+      <c r="D13" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>363</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>331</v>
+      </c>
+      <c r="D14" t="s">
+        <v>364</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>